--- a/data/trans_orig/P74B-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P74B-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su pareja percibe algún tipo de pensión en 2007</t>
+          <t>Población según si su pareja percibe algún tipo de pensión en 2007 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4529</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15126</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29161</t>
+          <t>28166</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35157</t>
+          <t>35142</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31195</t>
+          <t>31878</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51745</t>
+          <t>52852</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,76%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81312</t>
+          <t>81794</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92391</t>
+          <t>92449</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>871</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81188</t>
+          <t>80081</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101738</t>
+          <t>101055</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,02%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>6402</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21414</t>
+          <t>21431</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62412</t>
+          <t>62815</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77682</t>
+          <t>79135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68690</t>
+          <t>68838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100508</t>
+          <t>99512</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>216418</t>
+          <t>216401</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>231634</t>
+          <t>231430</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13774</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29044</t>
+          <t>28641</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>228780</t>
+          <t>229776</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>260598</t>
+          <t>260450</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,1%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11167</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42366</t>
+          <t>42173</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53171</t>
+          <t>53136</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41720</t>
+          <t>41294</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67080</t>
+          <t>66924</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,0%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>134484</t>
+          <t>133901</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143779</t>
+          <t>143727</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14779</t>
+          <t>14972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135716</t>
+          <t>135872</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>161076</t>
+          <t>161502</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13222</t>
+          <t>13473</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28841</t>
+          <t>29185</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51974</t>
+          <t>51015</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63385</t>
+          <t>63396</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64775</t>
+          <t>66368</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91507</t>
+          <t>92265</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,59%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117956</t>
+          <t>117612</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133575</t>
+          <t>133324</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17890</t>
+          <t>18849</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125154</t>
+          <t>124396</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>151886</t>
+          <t>150293</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16114</t>
+          <t>16945</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32502</t>
+          <t>31134</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42903</t>
+          <t>42963</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37074</t>
+          <t>37896</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58467</t>
+          <t>59726</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>48,77%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60339</t>
+          <t>59508</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72085</t>
+          <t>72214</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>14873</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63993</t>
+          <t>62734</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>85386</t>
+          <t>84564</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,05%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>977</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>9890</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43096</t>
+          <t>43499</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54352</t>
+          <t>55128</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42209</t>
+          <t>43226</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67808</t>
+          <t>68119</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,91%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>126275</t>
+          <t>125144</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>134040</t>
+          <t>134057</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16987</t>
+          <t>16584</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>127308</t>
+          <t>126997</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>152907</t>
+          <t>151890</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>77,85%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14533</t>
+          <t>13928</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33166</t>
+          <t>32574</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>85294</t>
+          <t>86138</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>102824</t>
+          <t>103496</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>73,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>100052</t>
+          <t>101439</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>136330</t>
+          <t>136804</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,82%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>230983</t>
+          <t>231575</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>249616</t>
+          <t>250221</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14945</t>
+          <t>14273</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32475</t>
+          <t>31631</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>245588</t>
+          <t>245114</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>281866</t>
+          <t>280479</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,44%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18023</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39121</t>
+          <t>36725</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>99991</t>
+          <t>101858</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>118944</t>
+          <t>119791</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>118821</t>
+          <t>118426</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>156852</t>
+          <t>156606</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,08%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>273556</t>
+          <t>275952</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>294654</t>
+          <t>294988</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>14795</t>
+          <t>13948</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>33748</t>
+          <t>31881</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>289564</t>
+          <t>289810</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>327595</t>
+          <t>327990</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,47%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>87757</t>
+          <t>87341</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>128470</t>
+          <t>128270</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>488369</t>
+          <t>487602</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>524803</t>
+          <t>524709</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>574679</t>
+          <t>573623</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>654034</t>
+          <t>658317</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1287042</t>
+          <t>1287242</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1327755</t>
+          <t>1328171</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>87273</t>
+          <t>87367</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>123707</t>
+          <t>124474</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1373554</t>
+          <t>1369271</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1452909</t>
+          <t>1453965</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su pareja percibe algún tipo de pensión en 2012</t>
+          <t>Población según si su pareja percibe algún tipo de pensión en 2012 (tasa de respuesta: 97,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16484</t>
+          <t>15932</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35938</t>
+          <t>35150</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37388</t>
+          <t>37766</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53928</t>
+          <t>53571</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58305</t>
+          <t>58185</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84709</t>
+          <t>84931</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,07%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54487</t>
+          <t>55275</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73941</t>
+          <t>74493</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12732</t>
+          <t>13089</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29272</t>
+          <t>28894</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72375</t>
+          <t>72153</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98779</t>
+          <t>98899</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,96%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11030</t>
+          <t>11492</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29202</t>
+          <t>29872</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87913</t>
+          <t>87764</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110781</t>
+          <t>110172</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99676</t>
+          <t>100156</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137019</t>
+          <t>137822</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>194652</t>
+          <t>193982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>212824</t>
+          <t>212362</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>34774</t>
+          <t>35383</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57642</t>
+          <t>57791</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>232390</t>
+          <t>231587</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>269733</t>
+          <t>269253</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,91%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,89%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21457</t>
+          <t>21164</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39192</t>
+          <t>39049</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55233</t>
+          <t>54796</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47242</t>
+          <t>48247</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74631</t>
+          <t>74921</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,01%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118168</t>
+          <t>118461</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131592</t>
+          <t>131926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13194</t>
+          <t>13631</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29235</t>
+          <t>29378</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133421</t>
+          <t>133131</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>160810</t>
+          <t>159805</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>76,81%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18220</t>
+          <t>18921</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38035</t>
+          <t>38959</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65493</t>
+          <t>66255</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81438</t>
+          <t>81483</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87575</t>
+          <t>87450</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118426</t>
+          <t>119040</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94427</t>
+          <t>93503</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114242</t>
+          <t>113541</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13375</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29320</t>
+          <t>28558</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>108849</t>
+          <t>108235</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>139700</t>
+          <t>139825</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,52%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>7667</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21456</t>
+          <t>21779</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35055</t>
+          <t>35164</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50352</t>
+          <t>50611</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44700</t>
+          <t>44977</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69551</t>
+          <t>69414</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>47,44%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60661</t>
+          <t>60338</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75353</t>
+          <t>74450</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13838</t>
+          <t>13579</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29135</t>
+          <t>29026</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>76756</t>
+          <t>76893</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101607</t>
+          <t>101330</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19422</t>
+          <t>18275</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41248</t>
+          <t>41574</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60383</t>
+          <t>59854</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49751</t>
+          <t>49893</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75702</t>
+          <t>75990</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,91%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>98425</t>
+          <t>99572</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111677</t>
+          <t>111862</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27629</t>
+          <t>28158</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46764</t>
+          <t>46438</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>130157</t>
+          <t>129869</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>156108</t>
+          <t>155966</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,76%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24181</t>
+          <t>24070</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47185</t>
+          <t>47062</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>104989</t>
+          <t>107494</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>132002</t>
+          <t>132493</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,33%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>133733</t>
+          <t>133916</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>176628</t>
+          <t>177402</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>40,01%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>216212</t>
+          <t>216335</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>239216</t>
+          <t>239327</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>48004</t>
+          <t>47513</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>75017</t>
+          <t>72512</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>266775</t>
+          <t>266001</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>309670</t>
+          <t>309487</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,8%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>20178</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40743</t>
+          <t>42208</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>127835</t>
+          <t>128761</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>156484</t>
+          <t>156903</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>148488</t>
+          <t>151810</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>193922</t>
+          <t>197033</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,72%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>284879</t>
+          <t>283414</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>306068</t>
+          <t>305444</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54546</t>
+          <t>54127</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>83195</t>
+          <t>82269</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>342730</t>
+          <t>339619</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>388164</t>
+          <t>384842</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>148641</t>
+          <t>148660</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>200744</t>
+          <t>199512</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>594825</t>
+          <t>595942</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>651059</t>
+          <t>654384</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>750687</t>
+          <t>753662</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>845000</t>
+          <t>847521</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,94%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1174605</t>
+          <t>1175837</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1226708</t>
+          <t>1226689</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>267632</t>
+          <t>264307</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>323866</t>
+          <t>322749</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1449040</t>
+          <t>1446519</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1543353</t>
+          <t>1540378</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,15%</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su pareja percibe algún tipo de pensión en 2016</t>
+          <t>Población según si su pareja percibe algún tipo de pensión en 2016 (tasa de respuesta: 94,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11085</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26385</t>
+          <t>26500</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22784</t>
+          <t>23962</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40533</t>
+          <t>41090</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38631</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62648</t>
+          <t>62641</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74680</t>
+          <t>74565</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89980</t>
+          <t>90777</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26671</t>
+          <t>26114</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44420</t>
+          <t>43242</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105622</t>
+          <t>105629</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>129639</t>
+          <t>129566</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,0%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24963</t>
+          <t>25441</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90145</t>
+          <t>89735</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113921</t>
+          <t>113578</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99842</t>
+          <t>99367</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137593</t>
+          <t>136406</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230293</t>
+          <t>229815</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>246241</t>
+          <t>246491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45875</t>
+          <t>46218</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69651</t>
+          <t>70061</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>277459</t>
+          <t>278646</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>315210</t>
+          <t>315685</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>76,06%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10851</t>
+          <t>10955</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26138</t>
+          <t>27538</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38979</t>
+          <t>40193</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56530</t>
+          <t>57050</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53804</t>
+          <t>53274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79983</t>
+          <t>80482</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,34%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>112593</t>
+          <t>111193</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127880</t>
+          <t>127776</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20301</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37852</t>
+          <t>36638</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135580</t>
+          <t>135081</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>161759</t>
+          <t>162289</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,29%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18271</t>
+          <t>19167</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36805</t>
+          <t>37563</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75400</t>
+          <t>75477</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97504</t>
+          <t>96972</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98001</t>
+          <t>98511</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131859</t>
+          <t>130769</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,58%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>119906</t>
+          <t>119148</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>138440</t>
+          <t>137544</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26552</t>
+          <t>27084</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48656</t>
+          <t>48579</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>148908</t>
+          <t>149998</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182766</t>
+          <t>182256</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,91%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>14873</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30936</t>
+          <t>30659</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35826</t>
+          <t>35124</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51447</t>
+          <t>51208</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54018</t>
+          <t>52977</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79326</t>
+          <t>76743</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>46,94%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61354</t>
+          <t>61631</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77767</t>
+          <t>77417</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19755</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>35376</t>
+          <t>36078</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84167</t>
+          <t>86750</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>109475</t>
+          <t>110516</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,6%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9390</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41316</t>
+          <t>41115</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57528</t>
+          <t>57310</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41575</t>
+          <t>42769</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66686</t>
+          <t>67618</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85327</t>
+          <t>84787</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93697</t>
+          <t>93712</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12933</t>
+          <t>13151</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29145</t>
+          <t>29346</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>98492</t>
+          <t>97560</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>123603</t>
+          <t>122409</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,11%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>13926</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32994</t>
+          <t>33306</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>82030</t>
+          <t>83230</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>106285</t>
+          <t>106701</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>97496</t>
+          <t>97638</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>136116</t>
+          <t>135611</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>36,73%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>196174</t>
+          <t>195862</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>214686</t>
+          <t>215242</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33804</t>
+          <t>33388</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>58059</t>
+          <t>56859</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>233142</t>
+          <t>233647</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>271762</t>
+          <t>271620</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,56%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32583</t>
+          <t>33295</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56692</t>
+          <t>56711</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>119344</t>
+          <t>120551</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>145046</t>
+          <t>146252</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>155404</t>
+          <t>156956</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>197533</t>
+          <t>198400</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,62%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>233207</t>
+          <t>233188</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>257316</t>
+          <t>256604</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9912,7 +9912,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>41712</t>
+          <t>40506</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67414</t>
+          <t>66207</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>279124</t>
+          <t>278257</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>321253</t>
+          <t>319701</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,07%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>145447</t>
+          <t>147024</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>194464</t>
+          <t>194003</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>561515</t>
+          <t>564336</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>621681</t>
+          <t>621389</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>718371</t>
+          <t>720959</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>813686</t>
+          <t>811145</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1163375</t>
+          <t>1163836</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1212392</t>
+          <t>1210815</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>274716</t>
+          <t>275008</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>334882</t>
+          <t>332061</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1440551</t>
+          <t>1443092</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1535866</t>
+          <t>1533278</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>68,02%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P74B-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P74B-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>14847</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28166</t>
+          <t>28517</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35142</t>
+          <t>35159</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31878</t>
+          <t>30892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52852</t>
+          <t>51978</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,1%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81794</t>
+          <t>82073</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92449</t>
+          <t>93231</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80081</t>
+          <t>80955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101055</t>
+          <t>102041</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,76%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21431</t>
+          <t>20724</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62815</t>
+          <t>63683</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79135</t>
+          <t>78420</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68838</t>
+          <t>68754</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99512</t>
+          <t>99559</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,23%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>216401</t>
+          <t>217108</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>231430</t>
+          <t>231665</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12321</t>
+          <t>13036</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28641</t>
+          <t>27773</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>229776</t>
+          <t>229729</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>260450</t>
+          <t>260534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,12%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11750</t>
+          <t>11972</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42173</t>
+          <t>42517</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53136</t>
+          <t>53156</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41294</t>
+          <t>41912</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66924</t>
+          <t>67654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,36%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133901</t>
+          <t>133679</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143727</t>
+          <t>143722</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14972</t>
+          <t>14628</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135872</t>
+          <t>135142</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>161502</t>
+          <t>160884</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,33%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>13379</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29185</t>
+          <t>29284</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51015</t>
+          <t>51913</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63396</t>
+          <t>63383</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>66368</t>
+          <t>66345</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>92265</t>
+          <t>93631</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>43,22%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117612</t>
+          <t>117513</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133324</t>
+          <t>133418</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18849</t>
+          <t>17951</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124396</t>
+          <t>123030</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>150293</t>
+          <t>150316</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,38%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4239</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16945</t>
+          <t>16384</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31134</t>
+          <t>32300</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42963</t>
+          <t>42951</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37896</t>
+          <t>37317</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59726</t>
+          <t>58482</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59508</t>
+          <t>60069</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72214</t>
+          <t>72127</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14873</t>
+          <t>13707</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62734</t>
+          <t>63978</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>84564</t>
+          <t>85143</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>69,53%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>982</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>8885</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43499</t>
+          <t>43430</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55128</t>
+          <t>55037</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43226</t>
+          <t>42793</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68119</t>
+          <t>67122</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>125144</t>
+          <t>126149</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>134057</t>
+          <t>134052</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4955</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16584</t>
+          <t>16653</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>126997</t>
+          <t>127994</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>151890</t>
+          <t>152323</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>78,07%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>13951</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32574</t>
+          <t>32067</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>86138</t>
+          <t>85558</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>103496</t>
+          <t>103511</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101439</t>
+          <t>100872</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>136804</t>
+          <t>136002</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>231575</t>
+          <t>232082</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>250221</t>
+          <t>250198</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14273</t>
+          <t>14258</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>31631</t>
+          <t>32211</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>245114</t>
+          <t>245916</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>280479</t>
+          <t>281046</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>18174</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36725</t>
+          <t>39686</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>101858</t>
+          <t>102056</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>119791</t>
+          <t>119344</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>118426</t>
+          <t>120576</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>156606</t>
+          <t>159525</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,73%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>275952</t>
+          <t>272991</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>294988</t>
+          <t>294503</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>14395</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>31881</t>
+          <t>31683</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>289810</t>
+          <t>286891</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>327990</t>
+          <t>325840</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>72,99%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>87341</t>
+          <t>88479</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>128270</t>
+          <t>128871</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>487602</t>
+          <t>486902</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>524709</t>
+          <t>525540</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>573623</t>
+          <t>573265</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>658317</t>
+          <t>654471</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1287242</t>
+          <t>1286641</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1328171</t>
+          <t>1327033</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>87367</t>
+          <t>86536</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>124474</t>
+          <t>125174</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1369271</t>
+          <t>1373117</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1453965</t>
+          <t>1454323</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,73%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15932</t>
+          <t>16076</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35150</t>
+          <t>36233</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37766</t>
+          <t>36112</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53571</t>
+          <t>53176</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58185</t>
+          <t>59105</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84931</t>
+          <t>86080</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,8%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55275</t>
+          <t>54192</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74493</t>
+          <t>74349</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13089</t>
+          <t>13484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28894</t>
+          <t>30548</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>72153</t>
+          <t>71004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98899</t>
+          <t>97979</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,37%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11492</t>
+          <t>11010</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29872</t>
+          <t>31224</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87764</t>
+          <t>87787</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110172</t>
+          <t>109673</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100156</t>
+          <t>101252</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137822</t>
+          <t>137827</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>193982</t>
+          <t>192630</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>212362</t>
+          <t>212844</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>35383</t>
+          <t>35882</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57791</t>
+          <t>57768</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>231587</t>
+          <t>231582</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>269253</t>
+          <t>268157</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>72,59%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>7883</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21164</t>
+          <t>20970</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39049</t>
+          <t>40003</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54796</t>
+          <t>55099</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48247</t>
+          <t>48116</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74921</t>
+          <t>74974</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118461</t>
+          <t>118655</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131926</t>
+          <t>131742</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13631</t>
+          <t>13328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29378</t>
+          <t>28424</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133131</t>
+          <t>133078</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>159805</t>
+          <t>159936</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,87%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18921</t>
+          <t>18016</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38959</t>
+          <t>37703</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66255</t>
+          <t>65272</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81483</t>
+          <t>81873</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>68,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87450</t>
+          <t>85391</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119040</t>
+          <t>117569</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>51,73%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93503</t>
+          <t>94759</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113541</t>
+          <t>114446</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13330</t>
+          <t>12940</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28558</t>
+          <t>29541</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>108235</t>
+          <t>109706</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>139825</t>
+          <t>141884</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>62,43%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7667</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21779</t>
+          <t>20981</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35164</t>
+          <t>34767</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50611</t>
+          <t>49860</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44977</t>
+          <t>43825</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69414</t>
+          <t>69041</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,19%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>60338</t>
+          <t>61136</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74450</t>
+          <t>75434</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13579</t>
+          <t>14330</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29026</t>
+          <t>29423</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>76893</t>
+          <t>77266</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>101330</t>
+          <t>102482</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>70,05%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>5689</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18275</t>
+          <t>17705</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41574</t>
+          <t>41265</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59854</t>
+          <t>60078</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49893</t>
+          <t>48690</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>75990</t>
+          <t>77180</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>99572</t>
+          <t>100142</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111862</t>
+          <t>112158</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28158</t>
+          <t>27934</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46438</t>
+          <t>46747</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>129869</t>
+          <t>128679</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>155966</t>
+          <t>157169</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,35%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24070</t>
+          <t>24208</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47062</t>
+          <t>48175</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>107494</t>
+          <t>107215</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>132493</t>
+          <t>133339</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>133916</t>
+          <t>135080</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>177402</t>
+          <t>176734</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,86%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>216335</t>
+          <t>215222</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>239327</t>
+          <t>239189</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>47513</t>
+          <t>46667</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>72512</t>
+          <t>72791</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>266001</t>
+          <t>266669</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>309487</t>
+          <t>308323</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,54%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20178</t>
+          <t>19894</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42208</t>
+          <t>41794</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>128761</t>
+          <t>128303</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>156903</t>
+          <t>156262</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>151810</t>
+          <t>151924</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>197033</t>
+          <t>194121</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>283414</t>
+          <t>283828</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>305444</t>
+          <t>305728</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>54127</t>
+          <t>54768</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>82269</t>
+          <t>82727</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>339619</t>
+          <t>342531</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>384842</t>
+          <t>384728</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,69%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>148660</t>
+          <t>147863</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>199512</t>
+          <t>200353</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>595942</t>
+          <t>596811</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>654384</t>
+          <t>652904</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>753662</t>
+          <t>752333</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>847521</t>
+          <t>845417</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1175837</t>
+          <t>1174996</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1226689</t>
+          <t>1227486</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>264307</t>
+          <t>265787</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>322749</t>
+          <t>321880</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1446519</t>
+          <t>1448623</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1540378</t>
+          <t>1541707</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,2%</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26500</t>
+          <t>26805</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23962</t>
+          <t>23761</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41090</t>
+          <t>40311</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>36484</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62641</t>
+          <t>62451</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74565</t>
+          <t>74260</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90777</t>
+          <t>90375</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26114</t>
+          <t>26893</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43242</t>
+          <t>43443</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>105629</t>
+          <t>105819</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>129566</t>
+          <t>131786</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>78,32%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8765</t>
+          <t>8555</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25441</t>
+          <t>24553</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89735</t>
+          <t>87755</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113578</t>
+          <t>115278</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99367</t>
+          <t>100401</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136406</t>
+          <t>138368</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,34%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>229815</t>
+          <t>230703</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>246491</t>
+          <t>246701</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46218</t>
+          <t>44518</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70061</t>
+          <t>72041</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>278646</t>
+          <t>276684</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>315685</t>
+          <t>314651</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,81%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10955</t>
+          <t>10829</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27538</t>
+          <t>27101</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40193</t>
+          <t>40427</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57050</t>
+          <t>57100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8114,12 +8114,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>53274</t>
+          <t>53603</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80482</t>
+          <t>80590</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>111193</t>
+          <t>111630</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127776</t>
+          <t>127902</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,12 +8192,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19781</t>
+          <t>19731</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36638</t>
+          <t>36404</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>135081</t>
+          <t>134973</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>162289</t>
+          <t>161960</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>75,13%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37563</t>
+          <t>37202</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75477</t>
+          <t>75913</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96972</t>
+          <t>97348</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>98511</t>
+          <t>98393</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130769</t>
+          <t>132745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>47,28%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>119148</t>
+          <t>119509</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>137544</t>
+          <t>137904</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27084</t>
+          <t>26708</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48579</t>
+          <t>48143</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149998</t>
+          <t>148022</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182256</t>
+          <t>182374</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>64,96%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14873</t>
+          <t>14969</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>30659</t>
+          <t>31274</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35124</t>
+          <t>35136</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51208</t>
+          <t>51025</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52977</t>
+          <t>52526</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76743</t>
+          <t>76513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61631</t>
+          <t>61016</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77417</t>
+          <t>77321</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19994</t>
+          <t>20177</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36078</t>
+          <t>36066</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>86750</t>
+          <t>86980</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>110516</t>
+          <t>110967</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,87%</t>
         </is>
       </c>
     </row>
@@ -9093,12 +9093,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9930</t>
+          <t>10135</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41115</t>
+          <t>40719</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>57310</t>
+          <t>57536</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42769</t>
+          <t>42254</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67618</t>
+          <t>67224</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,7%</t>
         </is>
       </c>
     </row>
@@ -9206,12 +9206,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>84787</t>
+          <t>84582</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93712</t>
+          <t>93678</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13151</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29346</t>
+          <t>29742</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>97560</t>
+          <t>97954</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>122409</t>
+          <t>122924</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,42%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13926</t>
+          <t>14219</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33306</t>
+          <t>34055</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83230</t>
+          <t>82327</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>106701</t>
+          <t>105690</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>97638</t>
+          <t>99811</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>135611</t>
+          <t>137777</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>195862</t>
+          <t>195113</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>215242</t>
+          <t>214949</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33388</t>
+          <t>34399</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>56859</t>
+          <t>57762</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>233647</t>
+          <t>231481</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>271620</t>
+          <t>269447</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>72,97%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33295</t>
+          <t>31736</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56711</t>
+          <t>57252</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>120551</t>
+          <t>119940</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>146252</t>
+          <t>145701</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>156956</t>
+          <t>155963</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>198400</t>
+          <t>200276</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>42,02%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>233188</t>
+          <t>232647</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>256604</t>
+          <t>258163</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40506</t>
+          <t>41057</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66207</t>
+          <t>66818</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>278257</t>
+          <t>276381</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>319701</t>
+          <t>320694</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>67,28%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>147024</t>
+          <t>146154</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>194003</t>
+          <t>195350</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>564336</t>
+          <t>563374</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>621389</t>
+          <t>623986</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>720959</t>
+          <t>715239</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>811145</t>
+          <t>803734</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1163836</t>
+          <t>1162489</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1210815</t>
+          <t>1211685</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>275008</t>
+          <t>272411</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>332061</t>
+          <t>333023</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1443092</t>
+          <t>1450503</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1533278</t>
+          <t>1538998</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,27%</t>
         </is>
       </c>
     </row>
